--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484578_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484578_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4504</v>
+        <v>7.2772</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9014</v>
+        <v>6.8769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.549</v>
+        <v>0.4004</v>
       </c>
       <c r="G2" t="n">
         <v>1.0518</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3254</v>
+        <v>-0.4985</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4864</v>
+        <v>-0.5109</v>
       </c>
       <c r="U2" t="n">
-        <v>0.161</v>
+        <v>0.0124</v>
       </c>
       <c r="V2" t="n">
         <v>4.8914</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.408</v>
+        <v>3.7271</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5269</v>
+        <v>3.7716</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1189</v>
+        <v>-0.0445</v>
       </c>
       <c r="G3" t="n">
         <v>-0.886</v>
@@ -688,13 +688,13 @@
         <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4523</v>
+        <v>-0.2287</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7119</v>
+        <v>-0.0433</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2597</v>
+        <v>-0.1854</v>
       </c>
       <c r="V3" t="n">
         <v>3.9255</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2932</v>
+        <v>3.3102</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7638</v>
+        <v>3.533</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4706</v>
+        <v>-0.2229</v>
       </c>
       <c r="G4" t="n">
         <v>3.5322</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.052</v>
+        <v>-1.0351</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9909</v>
+        <v>-0.2217</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0611</v>
+        <v>-0.8134</v>
       </c>
       <c r="V4" t="n">
         <v>0.4466</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4104</v>
+        <v>2.0701</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5339</v>
+        <v>0.0019</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9443</v>
+        <v>2.0681</v>
       </c>
       <c r="G5" t="n">
         <v>0.6317</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1376</v>
+        <v>0.5221</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5505</v>
+        <v>-0.0147</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4129</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3685</v>
+        <v>0.7804</v>
       </c>
       <c r="E7" t="n">
-        <v>0.851</v>
+        <v>1.3868</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4825</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.5556</v>
@@ -1000,13 +1000,13 @@
         <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5584</v>
+        <v>-0.1465</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.101</v>
+        <v>-0.5652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5426</v>
+        <v>0.4187</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8277</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4371</v>
+        <v>-0.1347</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9237</v>
+        <v>-2.6213</v>
       </c>
       <c r="F11" t="n">
         <v>2.4866</v>
@@ -1312,10 +1312,10 @@
         <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1094</v>
+        <v>0.1931</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3499</v>
+        <v>-0.0475</v>
       </c>
       <c r="U11" t="n">
         <v>0.2405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0587</v>
+        <v>-2.1441</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9381</v>
+        <v>-1.8996</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1206</v>
+        <v>-0.2445</v>
       </c>
       <c r="G12" t="n">
         <v>0.07149999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9144</v>
+        <v>0.829</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4276</v>
+        <v>0.4661</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4868</v>
+        <v>0.3629</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5785</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3091</v>
+        <v>-3.0119</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.442</v>
+        <v>-2.2935</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.867</v>
+        <v>-0.7184</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2545</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.538</v>
+        <v>-0.1648</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9322</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3941</v>
+        <v>-0.2455</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1424</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.053</v>
+        <v>-4.2511</v>
       </c>
       <c r="E14" t="n">
         <v>-2.5863</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4666</v>
+        <v>-1.6648</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6441</v>
@@ -1546,13 +1546,13 @@
         <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5466</v>
+        <v>0.3484</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0746</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6212</v>
+        <v>0.4231</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8559</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.842899999999997</v>
+        <v>9.3935</v>
       </c>
       <c r="E15" t="n">
-        <v>7.261200000000001</v>
+        <v>7.8116</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5819</v>
+        <v>1.5818</v>
       </c>
       <c r="G15" t="n">
         <v>3.6479</v>
@@ -1624,13 +1624,13 @@
         <v>17.4093</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7315</v>
+        <v>-0.1809999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4816</v>
+        <v>-0.9311</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7501000000000001</v>
+        <v>0.7501</v>
       </c>
       <c r="V15" t="n">
         <v>3.177899999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3963</v>
+        <v>4.8413</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6302</v>
+        <v>4.1494</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7662</v>
+        <v>0.6918</v>
       </c>
       <c r="G16" t="n">
         <v>5.4649</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1043</v>
+        <v>0.5492</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5649</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5394</v>
+        <v>0.4651</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6231</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.001</v>
+        <v>2.5509</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7265</v>
+        <v>3.0534</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7255</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>1.2564</v>
@@ -1780,13 +1780,13 @@
         <v>0.3665</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4043</v>
+        <v>-0.0458</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.2236</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4924</v>
+        <v>-0.2694</v>
       </c>
       <c r="V17" t="n">
         <v>1.89</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>P. MORTE MONTAÑES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.628</v>
+        <v>0.3251</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8187</v>
+        <v>0.3251</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4467</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4361</v>
+        <v>0.3251</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1859</v>
+        <v>0.3251</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6219</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.906</v>
+        <v>0.3251</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8545</v>
+        <v>0.3251</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3421</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6686</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6735</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6139</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2911</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3227</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MORTE MONTAÑES</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3251</v>
+        <v>0.1607</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3251</v>
+        <v>0.8665</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.7058</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3251</v>
+        <v>1.4573</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3251</v>
+        <v>1.3005</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.1568</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3251</v>
+        <v>2.3109</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3251</v>
+        <v>2.1858</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.8535</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.8854</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.0318</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.2521</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.2949</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.0428</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5993</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>G. VOLPATO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0368</v>
+        <v>-0.0041</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8665</v>
+        <v>0.2617</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8297</v>
+        <v>-0.2658</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4573</v>
+        <v>-1.1129</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3005</v>
+        <v>-0.3182</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1568</v>
+        <v>-0.7947</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3109</v>
+        <v>0.2764</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1858</v>
+        <v>0.1734</v>
       </c>
       <c r="L21" t="n">
-        <v>0.125</v>
+        <v>0.103</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8535</v>
+        <v>-1.3893</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8854</v>
+        <v>-0.4916</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0318</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3759</v>
+        <v>-0.174</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2949</v>
+        <v>-0.0147</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.1593</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5993</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. VOLPATO</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6087</v>
+        <v>-0.8844</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.219</v>
+        <v>-1.5879</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3897</v>
+        <v>0.7035</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1129</v>
+        <v>-0.4361</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3182</v>
+        <v>0.1859</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7947</v>
+        <v>-0.6219</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2764</v>
+        <v>0.906</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1734</v>
+        <v>0.8545</v>
       </c>
       <c r="L22" t="n">
-        <v>0.103</v>
+        <v>0.0515</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3893</v>
+        <v>-1.3421</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4916</v>
+        <v>-0.6686</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.6735</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2828</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7786999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4955</v>
+        <v>-0.4781</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2832</v>
+        <v>0.5795</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1592</v>
+        <v>-1.1344</v>
       </c>
       <c r="E23" t="n">
         <v>-0.6704</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4888</v>
+        <v>-0.464</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1493</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0936</v>
+        <v>-0.0688</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2629</v>
+        <v>-1.2359</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5602</v>
+        <v>-2.4429</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2973</v>
+        <v>1.207</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4021</v>
+        <v>-2.5405</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0272</v>
+        <v>-4.762</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.375</v>
+        <v>2.2215</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1929</v>
+        <v>-1.5267</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0217</v>
+        <v>-3.6202</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2146</v>
+        <v>2.0936</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2092</v>
+        <v>-1.0139</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0489</v>
+        <v>-1.1418</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1603</v>
+        <v>0.1279</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1833</v>
+        <v>2.5656</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8722</v>
+        <v>0.1318</v>
       </c>
       <c r="T24" t="n">
-        <v>0.549</v>
+        <v>-0.1674</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3232</v>
+        <v>0.2992</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5935</v>
+        <v>-1.305</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2204</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F25" t="n">
         <v>-1.3731</v>
@@ -2404,10 +2404,10 @@
         <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3846</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2753</v>
+        <v>0.0132</v>
       </c>
       <c r="U25" t="n">
         <v>-0.1094</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0257</v>
+        <v>-1.4618</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.155</v>
+        <v>-1.9627</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1293</v>
+        <v>0.5009</v>
       </c>
       <c r="G26" t="n">
         <v>-1.5947</v>
@@ -2482,13 +2482,13 @@
         <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4023</v>
+        <v>-0.8384</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9909</v>
+        <v>-0.7986</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4114</v>
+        <v>-0.0398</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3115</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.0417</v>
+        <v>-1.5077</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.8275</v>
+        <v>-1.6564</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7859</v>
+        <v>0.1486</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.5405</v>
+        <v>-1.4021</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.762</v>
+        <v>-0.0272</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2215</v>
+        <v>-1.375</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.5267</v>
+        <v>-1.1929</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.6202</v>
+        <v>0.0217</v>
       </c>
       <c r="L27" t="n">
-        <v>2.0936</v>
+        <v>-1.2146</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.0139</v>
+        <v>-0.2092</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.1418</v>
+        <v>-0.0489</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1279</v>
+        <v>-0.1603</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5656</v>
+        <v>0.1833</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.674</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.552</v>
+        <v>0.4529</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.122</v>
+        <v>0.1746</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.9464</v>
+        <v>-5.0425</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.1533</v>
+        <v>-3.2494</v>
       </c>
       <c r="F28" t="n">
         <v>-1.7931</v>
@@ -2638,10 +2638,10 @@
         <v>1.4661</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8243</v>
+        <v>0.7281</v>
       </c>
       <c r="T28" t="n">
-        <v>0.6395</v>
+        <v>0.5434</v>
       </c>
       <c r="U28" t="n">
         <v>0.1847</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.4927</v>
+        <v>-6.0455</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.406</v>
+        <v>-0.6368</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.0867</v>
+        <v>-5.4088</v>
       </c>
       <c r="G29" t="n">
         <v>-3.9915</v>
@@ -2716,13 +2716,13 @@
         <v>0.9163</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.3784</v>
+        <v>0.0688</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.9728</v>
+        <v>-0.2036</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5945</v>
+        <v>0.2724</v>
       </c>
       <c r="V29" t="n">
         <v>-2.8559</v>
@@ -2749,22 +2749,22 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-8.843100000000002</v>
+        <v>-8.842799999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.581699999999999</v>
+        <v>-1.5818</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.261200000000001</v>
+        <v>-7.2613</v>
       </c>
       <c r="G30" t="n">
-        <v>-3.647900000000001</v>
+        <v>-3.6479</v>
       </c>
       <c r="H30" t="n">
         <v>-3.647799999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>8.612400000000001</v>
@@ -2785,7 +2785,7 @@
         <v>-4.4901</v>
       </c>
       <c r="P30" t="n">
-        <v>-2.748900000000001</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q30" t="n">
         <v>-17.4095</v>
@@ -2794,13 +2794,13 @@
         <v>14.6607</v>
       </c>
       <c r="S30" t="n">
-        <v>0.7314999999999996</v>
+        <v>0.7315</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.7503000000000004</v>
+        <v>-0.7501999999999999</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4815</v>
+        <v>1.4817</v>
       </c>
       <c r="V30" t="n">
         <v>-3.1778</v>
